--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/70.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/70.xlsx
@@ -426,13 +426,13 @@
         <v>-4.781617394693794</v>
       </c>
       <c r="E2">
-        <v>-6.6306888166927</v>
+        <v>2.5308080780631</v>
       </c>
       <c r="F2">
-        <v>-4.802943103173473</v>
+        <v>-2.592564802076399</v>
       </c>
       <c r="G2">
-        <v>-6.222746987921714</v>
+        <v>-4.295656035065798</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-3.860046975930593</v>
       </c>
       <c r="E3">
-        <v>-6.687638905813163</v>
+        <v>1.889327092506556</v>
       </c>
       <c r="F3">
-        <v>-4.800648525467719</v>
+        <v>-2.470426998738029</v>
       </c>
       <c r="G3">
-        <v>-6.601094802276606</v>
+        <v>-2.609734866829068</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-3.140586350274128</v>
       </c>
       <c r="E4">
-        <v>-7.999411028563051</v>
+        <v>1.346806849439631</v>
       </c>
       <c r="F4">
-        <v>-4.769129145791198</v>
+        <v>-2.347128652668336</v>
       </c>
       <c r="G4">
-        <v>-6.434398903392136</v>
+        <v>-2.833258241901561</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-2.799137636737831</v>
       </c>
       <c r="E5">
-        <v>-7.633673353807562</v>
+        <v>0.9227062016732871</v>
       </c>
       <c r="F5">
-        <v>-4.873892771223251</v>
+        <v>-2.684527666032992</v>
       </c>
       <c r="G5">
-        <v>-6.282130535704545</v>
+        <v>-2.277931180294899</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-2.794417785632125</v>
       </c>
       <c r="E6">
-        <v>-9.190689514916846</v>
+        <v>-0.5074447601111115</v>
       </c>
       <c r="F6">
-        <v>-4.389413812021933</v>
+        <v>-2.44386456959986</v>
       </c>
       <c r="G6">
-        <v>-6.048920994588571</v>
+        <v>-2.76991754091804</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-3.091208885665051</v>
       </c>
       <c r="E7">
-        <v>-9.380586543954495</v>
+        <v>-0.6287263509845391</v>
       </c>
       <c r="F7">
-        <v>-4.643143575866824</v>
+        <v>-1.815104718015937</v>
       </c>
       <c r="G7">
-        <v>-5.80027330603541</v>
+        <v>-2.473035895441042</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-3.594571301001726</v>
       </c>
       <c r="E8">
-        <v>-10.51258730554788</v>
+        <v>-2.007624043950125</v>
       </c>
       <c r="F8">
-        <v>-4.590238234952228</v>
+        <v>-2.219174881794911</v>
       </c>
       <c r="G8">
-        <v>-5.782653146261192</v>
+        <v>-2.692336338366529</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-4.205085115966801</v>
       </c>
       <c r="E9">
-        <v>-10.578186780023</v>
+        <v>-1.573465655412744</v>
       </c>
       <c r="F9">
-        <v>-4.855269415273513</v>
+        <v>-2.160715337444544</v>
       </c>
       <c r="G9">
-        <v>-5.445284507962205</v>
+        <v>-2.51677129760688</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-4.805426339368264</v>
       </c>
       <c r="E10">
-        <v>-11.42771491843993</v>
+        <v>-2.774770183219522</v>
       </c>
       <c r="F10">
-        <v>-5.017370147225139</v>
+        <v>-2.119470096091753</v>
       </c>
       <c r="G10">
-        <v>-5.236077102553569</v>
+        <v>-0.9637756959648152</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.292927910290352</v>
       </c>
       <c r="E11">
-        <v>-11.50517899481514</v>
+        <v>-3.688013950924379</v>
       </c>
       <c r="F11">
-        <v>-4.750424609835985</v>
+        <v>-2.30710359649987</v>
       </c>
       <c r="G11">
-        <v>-4.986418797760099</v>
+        <v>-0.7725821969175309</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.580411924395242</v>
       </c>
       <c r="E12">
-        <v>-12.48965113018665</v>
+        <v>-4.567502473376063</v>
       </c>
       <c r="F12">
-        <v>-4.727061335607428</v>
+        <v>-1.888107908857255</v>
       </c>
       <c r="G12">
-        <v>-4.090035004821635</v>
+        <v>-1.425919346504806</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.617064457592519</v>
       </c>
       <c r="E13">
-        <v>-12.43284142376042</v>
+        <v>-5.643644508084838</v>
       </c>
       <c r="F13">
-        <v>-4.762288487778879</v>
+        <v>-1.885992258510504</v>
       </c>
       <c r="G13">
-        <v>-3.682622129893182</v>
+        <v>-0.1400151798015409</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-5.39402681394513</v>
       </c>
       <c r="E14">
-        <v>-14.04122859401272</v>
+        <v>-6.467808663584813</v>
       </c>
       <c r="F14">
-        <v>-4.961606938770886</v>
+        <v>-1.397847773551798</v>
       </c>
       <c r="G14">
-        <v>-3.044860939048591</v>
+        <v>0.3319032297640359</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.943785592394394</v>
       </c>
       <c r="E15">
-        <v>-14.73193862050665</v>
+        <v>-7.711653676219646</v>
       </c>
       <c r="F15">
-        <v>-4.586709389816302</v>
+        <v>-1.675525639011623</v>
       </c>
       <c r="G15">
-        <v>-1.875197327310214</v>
+        <v>0.9727520500960645</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.335599542356944</v>
       </c>
       <c r="E16">
-        <v>-15.56222527286499</v>
+        <v>-7.200619912928053</v>
       </c>
       <c r="F16">
-        <v>-4.946376575703014</v>
+        <v>-1.620589141225363</v>
       </c>
       <c r="G16">
-        <v>-1.489493014219047</v>
+        <v>2.13911475294564</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-3.664302359393254</v>
       </c>
       <c r="E17">
-        <v>-16.78229126848555</v>
+        <v>-8.837826291765163</v>
       </c>
       <c r="F17">
-        <v>-4.642998611571334</v>
+        <v>-1.282316200250754</v>
       </c>
       <c r="G17">
-        <v>-0.9309011371607385</v>
+        <v>2.410245371624116</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-3.038444276368705</v>
       </c>
       <c r="E18">
-        <v>-17.6212635339906</v>
+        <v>-10.02577634972332</v>
       </c>
       <c r="F18">
-        <v>-4.405424497183241</v>
+        <v>-0.9331601683381648</v>
       </c>
       <c r="G18">
-        <v>-0.8512232340327425</v>
+        <v>1.817998005030583</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-2.558986699109959</v>
       </c>
       <c r="E19">
-        <v>-18.30727300446457</v>
+        <v>-11.80216537718618</v>
       </c>
       <c r="F19">
-        <v>-4.050268600172176</v>
+        <v>-0.6874490009523727</v>
       </c>
       <c r="G19">
-        <v>-0.165323241689538</v>
+        <v>2.321081456967765</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-2.300025410227064</v>
       </c>
       <c r="E20">
-        <v>-18.61203024823277</v>
+        <v>-11.56517674694277</v>
       </c>
       <c r="F20">
-        <v>-3.750606692209455</v>
+        <v>-0.3838076159866027</v>
       </c>
       <c r="G20">
-        <v>-0.3300471264167816</v>
+        <v>3.375259194699926</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-2.296813355014387</v>
       </c>
       <c r="E21">
-        <v>-18.35779266049414</v>
+        <v>-12.34473543346719</v>
       </c>
       <c r="F21">
-        <v>-3.804415781960505</v>
+        <v>-0.2317359281806695</v>
       </c>
       <c r="G21">
-        <v>0.8547232293812785</v>
+        <v>2.976347964831994</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-2.54152502077476</v>
       </c>
       <c r="E22">
-        <v>-19.4989862243231</v>
+        <v>-13.26449114679508</v>
       </c>
       <c r="F22">
-        <v>-3.71939712194158</v>
+        <v>-0.1501334553308901</v>
       </c>
       <c r="G22">
-        <v>-0.5710561311795554</v>
+        <v>3.587265482098768</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.989547500055935</v>
       </c>
       <c r="E23">
-        <v>-19.64362115565408</v>
+        <v>-14.45210609767667</v>
       </c>
       <c r="F23">
-        <v>-3.283105951295914</v>
+        <v>0.628391909209572</v>
       </c>
       <c r="G23">
-        <v>-0.2099084802392728</v>
+        <v>3.410972010152922</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-3.568337276835168</v>
       </c>
       <c r="E24">
-        <v>-20.56427350683549</v>
+        <v>-15.15751102232548</v>
       </c>
       <c r="F24">
-        <v>-3.426196479720695</v>
+        <v>-0.008265597192641218</v>
       </c>
       <c r="G24">
-        <v>-0.2105122250062106</v>
+        <v>3.391717802042101</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.191008122456141</v>
       </c>
       <c r="E25">
-        <v>-20.70616418291783</v>
+        <v>-14.69761731600251</v>
       </c>
       <c r="F25">
-        <v>-2.935481570711102</v>
+        <v>0.6066240705988066</v>
       </c>
       <c r="G25">
-        <v>-0.9594871393866209</v>
+        <v>3.917651680919256</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.770571486014617</v>
       </c>
       <c r="E26">
-        <v>-20.44142959242942</v>
+        <v>-15.04992806532526</v>
       </c>
       <c r="F26">
-        <v>-3.006809802663959</v>
+        <v>0.6490331681525301</v>
       </c>
       <c r="G26">
-        <v>-0.6592422418111916</v>
+        <v>3.66271389063664</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-5.231683990197946</v>
       </c>
       <c r="E27">
-        <v>-20.3081113176436</v>
+        <v>-15.44880964134289</v>
       </c>
       <c r="F27">
-        <v>-2.87612987466792</v>
+        <v>0.5705014532649285</v>
       </c>
       <c r="G27">
-        <v>-1.510328771121521</v>
+        <v>2.967370542645353</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-5.521326251954401</v>
       </c>
       <c r="E28">
-        <v>-20.04382957455596</v>
+        <v>-15.91792784921948</v>
       </c>
       <c r="F28">
-        <v>-3.015408256305018</v>
+        <v>0.8499967568064958</v>
       </c>
       <c r="G28">
-        <v>-1.21447086677107</v>
+        <v>1.904248194942146</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.612264434445527</v>
       </c>
       <c r="E29">
-        <v>-20.56992957087107</v>
+        <v>-13.98164293301979</v>
       </c>
       <c r="F29">
-        <v>-2.965630830703393</v>
+        <v>0.4470896208610526</v>
       </c>
       <c r="G29">
-        <v>-1.693644057204579</v>
+        <v>1.832455067221496</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-5.503873557781684</v>
       </c>
       <c r="E30">
-        <v>-20.37905891992177</v>
+        <v>-14.18262566642822</v>
       </c>
       <c r="F30">
-        <v>-2.805591905217334</v>
+        <v>0.6271783509644707</v>
       </c>
       <c r="G30">
-        <v>-2.009983346529085</v>
+        <v>1.499309361069515</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-5.21973304186317</v>
       </c>
       <c r="E31">
-        <v>-20.18528098865955</v>
+        <v>-14.65200652579726</v>
       </c>
       <c r="F31">
-        <v>-2.799900192792698</v>
+        <v>0.5149188289044845</v>
       </c>
       <c r="G31">
-        <v>-2.028653497202325</v>
+        <v>2.317409770042747</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-4.803372128843348</v>
       </c>
       <c r="E32">
-        <v>-20.6679483907671</v>
+        <v>-12.52700651227592</v>
       </c>
       <c r="F32">
-        <v>-2.822886559852982</v>
+        <v>0.8040919488129583</v>
       </c>
       <c r="G32">
-        <v>-2.784476320977296</v>
+        <v>2.027162754558946</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-4.313188364847308</v>
       </c>
       <c r="E33">
-        <v>-19.57145539386785</v>
+        <v>-13.94182858954435</v>
       </c>
       <c r="F33">
-        <v>-2.864884787174917</v>
+        <v>0.7653773698757207</v>
       </c>
       <c r="G33">
-        <v>-2.487657018709927</v>
+        <v>1.996650675277669</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-3.81284214968721</v>
       </c>
       <c r="E34">
-        <v>-19.30898504038328</v>
+        <v>-13.04072113218005</v>
       </c>
       <c r="F34">
-        <v>-2.813559142897459</v>
+        <v>0.5441187798531671</v>
       </c>
       <c r="G34">
-        <v>-1.611160709643258</v>
+        <v>1.814316474440886</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-3.362848905979763</v>
       </c>
       <c r="E35">
-        <v>-19.31556038464241</v>
+        <v>-12.83681300456267</v>
       </c>
       <c r="F35">
-        <v>-2.672169252750626</v>
+        <v>0.3984072969659285</v>
       </c>
       <c r="G35">
-        <v>-2.463523634140211</v>
+        <v>1.85748422527694</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.011752411217834</v>
       </c>
       <c r="E36">
-        <v>-18.74757653223036</v>
+        <v>-11.21122669002924</v>
       </c>
       <c r="F36">
-        <v>-2.403275395230087</v>
+        <v>0.3616203289750052</v>
       </c>
       <c r="G36">
-        <v>-2.569818806558423</v>
+        <v>2.836804174351929</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-2.790931570677639</v>
       </c>
       <c r="E37">
-        <v>-18.6912196732049</v>
+        <v>-12.02078651685448</v>
       </c>
       <c r="F37">
-        <v>-2.842153557274695</v>
+        <v>0.7133567253473145</v>
       </c>
       <c r="G37">
-        <v>-2.546689475785897</v>
+        <v>1.549101898234088</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.713840625472963</v>
       </c>
       <c r="E38">
-        <v>-18.95303792643237</v>
+        <v>-11.69730403306457</v>
       </c>
       <c r="F38">
-        <v>-2.193410170465638</v>
+        <v>0.6948360869555231</v>
       </c>
       <c r="G38">
-        <v>-2.76383087492527</v>
+        <v>1.506419768188831</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.774129440532329</v>
       </c>
       <c r="E39">
-        <v>-17.31029322388388</v>
+        <v>-11.35539066006343</v>
       </c>
       <c r="F39">
-        <v>-2.407706332467661</v>
+        <v>0.9165179727209073</v>
       </c>
       <c r="G39">
-        <v>-2.697448481556144</v>
+        <v>2.385455742742511</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.950044273926857</v>
       </c>
       <c r="E40">
-        <v>-17.56428174555209</v>
+        <v>-10.94976618624838</v>
       </c>
       <c r="F40">
-        <v>-2.415877348528876</v>
+        <v>1.266031030984103</v>
       </c>
       <c r="G40">
-        <v>-2.568430849838778</v>
+        <v>2.419790445140541</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.208727514507008</v>
       </c>
       <c r="E41">
-        <v>-15.75754741376383</v>
+        <v>-9.686471377750603</v>
       </c>
       <c r="F41">
-        <v>-2.270857552422974</v>
+        <v>0.8984148315001269</v>
       </c>
       <c r="G41">
-        <v>-2.425320371523596</v>
+        <v>3.02334818244948</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.514672009134688</v>
       </c>
       <c r="E42">
-        <v>-16.75041533994555</v>
+        <v>-9.839280204665432</v>
       </c>
       <c r="F42">
-        <v>-2.172611521716147</v>
+        <v>0.3616004481573381</v>
       </c>
       <c r="G42">
-        <v>-2.370947249062038</v>
+        <v>2.400093272119194</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.835167741383557</v>
       </c>
       <c r="E43">
-        <v>-16.3237696897869</v>
+        <v>-7.848255094661022</v>
       </c>
       <c r="F43">
-        <v>-2.369641193574218</v>
+        <v>0.6203078717256516</v>
       </c>
       <c r="G43">
-        <v>-1.995539409224409</v>
+        <v>2.368698544238427</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.141714289848294</v>
       </c>
       <c r="E44">
-        <v>-15.37878131928827</v>
+        <v>-9.263946638938929</v>
       </c>
       <c r="F44">
-        <v>-2.510746125334489</v>
+        <v>0.4673357485528754</v>
       </c>
       <c r="G44">
-        <v>-1.815925341060405</v>
+        <v>3.131087092353847</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.411978787036424</v>
       </c>
       <c r="E45">
-        <v>-15.40530912002521</v>
+        <v>-8.863289901110294</v>
       </c>
       <c r="F45">
-        <v>-2.222398887726606</v>
+        <v>0.8119266477086361</v>
       </c>
       <c r="G45">
-        <v>-1.629141803789015</v>
+        <v>3.440509566631043</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.629616701227689</v>
       </c>
       <c r="E46">
-        <v>-15.46334604290751</v>
+        <v>-8.314552063230838</v>
       </c>
       <c r="F46">
-        <v>-2.533789649745565</v>
+        <v>0.7183642062972375</v>
       </c>
       <c r="G46">
-        <v>-1.328325973662242</v>
+        <v>3.250717149189642</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.787435324153866</v>
       </c>
       <c r="E47">
-        <v>-14.65104648930763</v>
+        <v>-7.597554245122383</v>
       </c>
       <c r="F47">
-        <v>-2.500946538959371</v>
+        <v>0.4554702138751752</v>
       </c>
       <c r="G47">
-        <v>-1.672135649882419</v>
+        <v>3.168351925604461</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.884558603574855</v>
       </c>
       <c r="E48">
-        <v>-14.32786741327623</v>
+        <v>-7.283115123925784</v>
       </c>
       <c r="F48">
-        <v>-2.616360484089217</v>
+        <v>0.5720529854103721</v>
       </c>
       <c r="G48">
-        <v>-0.9196662345411998</v>
+        <v>3.277062077090424</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.924486848893697</v>
       </c>
       <c r="E49">
-        <v>-13.71392860663434</v>
+        <v>-8.442037663494775</v>
       </c>
       <c r="F49">
-        <v>-2.519793554107865</v>
+        <v>0.2852291154562376</v>
       </c>
       <c r="G49">
-        <v>-1.782430631381593</v>
+        <v>3.908388792456944</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.914099035918436</v>
       </c>
       <c r="E50">
-        <v>-13.54516143731648</v>
+        <v>-7.103389047509363</v>
       </c>
       <c r="F50">
-        <v>-2.289759239820054</v>
+        <v>0.8639597177480842</v>
       </c>
       <c r="G50">
-        <v>-0.9358295319430245</v>
+        <v>3.898564815107966</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.863277763939603</v>
       </c>
       <c r="E51">
-        <v>-13.22389337731631</v>
+        <v>-5.385322236791291</v>
       </c>
       <c r="F51">
-        <v>-2.077296254880425</v>
+        <v>0.4565429496618006</v>
       </c>
       <c r="G51">
-        <v>-1.310036444689897</v>
+        <v>3.793175259840162</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.783993279508203</v>
       </c>
       <c r="E52">
-        <v>-13.1721691472007</v>
+        <v>-5.916059390490257</v>
       </c>
       <c r="F52">
-        <v>-2.270199000337749</v>
+        <v>0.6244041485324952</v>
       </c>
       <c r="G52">
-        <v>-1.358874146380672</v>
+        <v>3.621803620233483</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.686508529051424</v>
       </c>
       <c r="E53">
-        <v>-11.78724858380491</v>
+        <v>-4.500413130952426</v>
       </c>
       <c r="F53">
-        <v>-2.488891308146429</v>
+        <v>0.7625344129493128</v>
       </c>
       <c r="G53">
-        <v>-1.464004485145281</v>
+        <v>2.96195652707227</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.577871460019952</v>
       </c>
       <c r="E54">
-        <v>-11.728260681381</v>
+        <v>-3.728589078033106</v>
       </c>
       <c r="F54">
-        <v>-2.452464679975724</v>
+        <v>0.1426322940035251</v>
       </c>
       <c r="G54">
-        <v>-1.648123670510402</v>
+        <v>2.741793122876648</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.460084674239284</v>
       </c>
       <c r="E55">
-        <v>-11.78949923538673</v>
+        <v>-4.329223228040464</v>
       </c>
       <c r="F55">
-        <v>-2.051847979899021</v>
+        <v>0.3786573613483827</v>
       </c>
       <c r="G55">
-        <v>-1.848904898954384</v>
+        <v>3.283988735802412</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.328921356255664</v>
       </c>
       <c r="E56">
-        <v>-10.45007172187199</v>
+        <v>-3.535816468000586</v>
       </c>
       <c r="F56">
-        <v>-2.420995830710774</v>
+        <v>0.5714052021013828</v>
       </c>
       <c r="G56">
-        <v>-1.593812891258473</v>
+        <v>2.54535951299893</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.178310618395772</v>
       </c>
       <c r="E57">
-        <v>-10.53068761615654</v>
+        <v>-3.6932216960332</v>
       </c>
       <c r="F57">
-        <v>-2.19665985578682</v>
+        <v>0.6025451895074219</v>
       </c>
       <c r="G57">
-        <v>-1.86588850174607</v>
+        <v>2.345805461418181</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.003318135617003</v>
       </c>
       <c r="E58">
-        <v>-10.4872097372089</v>
+        <v>-2.758300123253624</v>
       </c>
       <c r="F58">
-        <v>-2.197058300507567</v>
+        <v>0.1315578501954985</v>
       </c>
       <c r="G58">
-        <v>-2.413120789765581</v>
+        <v>2.076791230645547</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-3.800619662966492</v>
       </c>
       <c r="E59">
-        <v>-10.84472370316646</v>
+        <v>-3.98542148137813</v>
       </c>
       <c r="F59">
-        <v>-2.251538367854884</v>
+        <v>0.7902598699210122</v>
       </c>
       <c r="G59">
-        <v>-2.843797525550497</v>
+        <v>2.26598318454157</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-3.569487352744266</v>
       </c>
       <c r="E60">
-        <v>-10.30404654902066</v>
+        <v>-2.543437617011689</v>
       </c>
       <c r="F60">
-        <v>-2.116441584867119</v>
+        <v>0.6468843831096682</v>
       </c>
       <c r="G60">
-        <v>-3.095906902848872</v>
+        <v>2.534095079385357</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-3.313140706905392</v>
       </c>
       <c r="E61">
-        <v>-10.03939347106439</v>
+        <v>-1.838327043173368</v>
       </c>
       <c r="F61">
-        <v>-1.857710967011527</v>
+        <v>0.5057910484930368</v>
       </c>
       <c r="G61">
-        <v>-3.110649431315458</v>
+        <v>1.640103296963728</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-3.04124688789364</v>
       </c>
       <c r="E62">
-        <v>-10.24236420456218</v>
+        <v>-1.790343332588093</v>
       </c>
       <c r="F62">
-        <v>-2.531866180636265</v>
+        <v>0.7752697333999523</v>
       </c>
       <c r="G62">
-        <v>-2.950388007909059</v>
+        <v>1.155555465615848</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-2.764169887440065</v>
       </c>
       <c r="E63">
-        <v>-9.250927276166877</v>
+        <v>-1.366885728130838</v>
       </c>
       <c r="F63">
-        <v>-1.784397138394159</v>
+        <v>0.6587938212597166</v>
       </c>
       <c r="G63">
-        <v>-3.460489992761894</v>
+        <v>0.8138654585230729</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-2.492641716845575</v>
       </c>
       <c r="E64">
-        <v>-9.383285514463067</v>
+        <v>-1.318403885404719</v>
       </c>
       <c r="F64">
-        <v>-2.075118476978465</v>
+        <v>0.6578817887492344</v>
       </c>
       <c r="G64">
-        <v>-3.168444867863517</v>
+        <v>1.423837983980727</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-2.239626264796176</v>
       </c>
       <c r="E65">
-        <v>-9.475752425225688</v>
+        <v>-2.38291227038779</v>
       </c>
       <c r="F65">
-        <v>-2.178060522491763</v>
+        <v>0.6355837950006773</v>
       </c>
       <c r="G65">
-        <v>-3.336089039778666</v>
+        <v>0.1521579127376544</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.020006949683248</v>
       </c>
       <c r="E66">
-        <v>-9.267709800839302</v>
+        <v>-1.075437669471181</v>
       </c>
       <c r="F66">
-        <v>-2.138505979008086</v>
+        <v>0.4562878125017383</v>
       </c>
       <c r="G66">
-        <v>-3.492983929865075</v>
+        <v>0.4049957212222264</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-1.849611509970662</v>
       </c>
       <c r="E67">
-        <v>-8.878772753742519</v>
+        <v>-1.681044083938961</v>
       </c>
       <c r="F67">
-        <v>-2.035056144276873</v>
+        <v>1.00016319958599</v>
       </c>
       <c r="G67">
-        <v>-3.825827763633587</v>
+        <v>0.7393128234709295</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-1.7418898367317</v>
       </c>
       <c r="E68">
-        <v>-8.391024403798367</v>
+        <v>-1.01352890131232</v>
       </c>
       <c r="F68">
-        <v>-2.425538597547726</v>
+        <v>0.3735811259040273</v>
       </c>
       <c r="G68">
-        <v>-4.464146762143284</v>
+        <v>-0.1526413203622842</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-1.707050280957244</v>
       </c>
       <c r="E69">
-        <v>-8.546735982552113</v>
+        <v>-0.2673269543283985</v>
       </c>
       <c r="F69">
-        <v>-2.183127645894687</v>
+        <v>0.4110382431238153</v>
       </c>
       <c r="G69">
-        <v>-3.953601812379924</v>
+        <v>-0.1173878759276102</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-1.748899272364921</v>
       </c>
       <c r="E70">
-        <v>-8.906482486195454</v>
+        <v>-0.0970518031659854</v>
       </c>
       <c r="F70">
-        <v>-2.448057765392831</v>
+        <v>0.41388617025464</v>
       </c>
       <c r="G70">
-        <v>-3.814904577062196</v>
+        <v>-0.1851877570104163</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-1.868543060422628</v>
       </c>
       <c r="E71">
-        <v>-8.876363605570438</v>
+        <v>0.116560844249833</v>
       </c>
       <c r="F71">
-        <v>-2.416699917359856</v>
+        <v>0.1450279325324213</v>
       </c>
       <c r="G71">
-        <v>-4.532957259466399</v>
+        <v>0.06455914076515878</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-2.063443986898163</v>
       </c>
       <c r="E72">
-        <v>-8.848816898181779</v>
+        <v>-0.34731339072588</v>
       </c>
       <c r="F72">
-        <v>-2.705866410329107</v>
+        <v>-0.2558016579668007</v>
       </c>
       <c r="G72">
-        <v>-4.28329239222981</v>
+        <v>-0.134164761761051</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-2.328906967501102</v>
       </c>
       <c r="E73">
-        <v>-9.185191947471534</v>
+        <v>-0.7486222288116194</v>
       </c>
       <c r="F73">
-        <v>-2.547079147988678</v>
+        <v>0.1313930050823414</v>
       </c>
       <c r="G73">
-        <v>-4.348509951945333</v>
+        <v>0.4571113632508868</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-2.659052500628851</v>
       </c>
       <c r="E74">
-        <v>-8.900568299141437</v>
+        <v>-0.4749982438461534</v>
       </c>
       <c r="F74">
-        <v>-2.907869600073586</v>
+        <v>0.0190233101577829</v>
       </c>
       <c r="G74">
-        <v>-4.405826330145714</v>
+        <v>-0.04099775680217773</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.046217777249978</v>
       </c>
       <c r="E75">
-        <v>-9.547216273540732</v>
+        <v>-0.6334812486925929</v>
       </c>
       <c r="F75">
-        <v>-2.843073873459206</v>
+        <v>0.2672021840365148</v>
       </c>
       <c r="G75">
-        <v>-3.567474221707589</v>
+        <v>0.5066512463553831</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.481547887789643</v>
       </c>
       <c r="E76">
-        <v>-8.567317896916975</v>
+        <v>-2.386516935697895</v>
       </c>
       <c r="F76">
-        <v>-2.740445779191569</v>
+        <v>-0.6021677484667608</v>
       </c>
       <c r="G76">
-        <v>-4.362350144483071</v>
+        <v>0.3994799877807998</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.950531139178222</v>
       </c>
       <c r="E77">
-        <v>-9.83065346168082</v>
+        <v>-2.5776275957696</v>
       </c>
       <c r="F77">
-        <v>-2.939951441216608</v>
+        <v>0.06842714206074541</v>
       </c>
       <c r="G77">
-        <v>-3.939919118477039</v>
+        <v>0.3892786699524862</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.435946289856225</v>
       </c>
       <c r="E78">
-        <v>-9.909598349056537</v>
+        <v>-1.192856472016066</v>
       </c>
       <c r="F78">
-        <v>-2.892938277638125</v>
+        <v>-0.2534018776008905</v>
       </c>
       <c r="G78">
-        <v>-3.727443616395197</v>
+        <v>0.7491236759336692</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.919552200306435</v>
       </c>
       <c r="E79">
-        <v>-11.20634046657497</v>
+        <v>-3.005029501087536</v>
       </c>
       <c r="F79">
-        <v>-3.337984463363979</v>
+        <v>-0.4519582305823208</v>
       </c>
       <c r="G79">
-        <v>-3.760764421331358</v>
+        <v>0.6768022715419483</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-5.381909783355114</v>
       </c>
       <c r="E80">
-        <v>-10.97188325330184</v>
+        <v>-4.004844106397028</v>
       </c>
       <c r="F80">
-        <v>-3.215455670611487</v>
+        <v>-0.6150703991327658</v>
       </c>
       <c r="G80">
-        <v>-3.523404134942687</v>
+        <v>0.5442474829835007</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-5.804231821793507</v>
       </c>
       <c r="E81">
-        <v>-11.87115215021903</v>
+        <v>-3.966990592166912</v>
       </c>
       <c r="F81">
-        <v>-3.136076535870822</v>
+        <v>-0.2836165786180025</v>
       </c>
       <c r="G81">
-        <v>-3.607672467032346</v>
+        <v>1.256932086916452</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.169207868309954</v>
       </c>
       <c r="E82">
-        <v>-11.54609828594845</v>
+        <v>-4.55794286474587</v>
       </c>
       <c r="F82">
-        <v>-3.187856125485013</v>
+        <v>-0.6222473743106208</v>
       </c>
       <c r="G82">
-        <v>-3.547229084685815</v>
+        <v>2.245249145507438</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.463745387402996</v>
       </c>
       <c r="E83">
-        <v>-12.7663363635813</v>
+        <v>-6.106676446895125</v>
       </c>
       <c r="F83">
-        <v>-3.625017910271021</v>
+        <v>-0.8242903256904341</v>
       </c>
       <c r="G83">
-        <v>-3.47410378101203</v>
+        <v>0.9943851438374834</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.681067825846316</v>
       </c>
       <c r="E84">
-        <v>-13.12630476245102</v>
+        <v>-6.232916716806952</v>
       </c>
       <c r="F84">
-        <v>-3.61075508032962</v>
+        <v>-0.3442025420913555</v>
       </c>
       <c r="G84">
-        <v>-3.675597034534411</v>
+        <v>1.680892162169185</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-6.822242325700085</v>
       </c>
       <c r="E85">
-        <v>-14.99014767995</v>
+        <v>-7.493236317881689</v>
       </c>
       <c r="F85">
-        <v>-3.50036766859996</v>
+        <v>-0.8343375939189894</v>
       </c>
       <c r="G85">
-        <v>-3.59996815881077</v>
+        <v>1.755664639065811</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-6.893970678122724</v>
       </c>
       <c r="E86">
-        <v>-16.13587424626064</v>
+        <v>-8.711984527566011</v>
       </c>
       <c r="F86">
-        <v>-3.747057137888459</v>
+        <v>-0.9957723184787655</v>
       </c>
       <c r="G86">
-        <v>-2.941669802225614</v>
+        <v>2.249918323786528</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-6.906003373095639</v>
       </c>
       <c r="E87">
-        <v>-16.7148441766153</v>
+        <v>-10.13614884671227</v>
       </c>
       <c r="F87">
-        <v>-3.965808259782738</v>
+        <v>-0.9634792436480295</v>
       </c>
       <c r="G87">
-        <v>-3.020967083652715</v>
+        <v>1.742086944252829</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-6.87137198060192</v>
       </c>
       <c r="E88">
-        <v>-18.11282938752322</v>
+        <v>-11.95111141577246</v>
       </c>
       <c r="F88">
-        <v>-3.67715452623582</v>
+        <v>-1.276071138401048</v>
       </c>
       <c r="G88">
-        <v>-3.38310566350395</v>
+        <v>2.249983948217717</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-6.804916566272558</v>
       </c>
       <c r="E89">
-        <v>-19.58987269765705</v>
+        <v>-13.52724679414213</v>
       </c>
       <c r="F89">
-        <v>-3.938974954503854</v>
+        <v>-1.190957216130802</v>
       </c>
       <c r="G89">
-        <v>-3.169734387936379</v>
+        <v>2.330889028208945</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-6.723996922852058</v>
       </c>
       <c r="E90">
-        <v>-20.39272132600292</v>
+        <v>-15.44381473451243</v>
       </c>
       <c r="F90">
-        <v>-3.704359768478561</v>
+        <v>-1.64005246172154</v>
       </c>
       <c r="G90">
-        <v>-3.32182885088132</v>
+        <v>2.040825761132473</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-6.646260916494573</v>
       </c>
       <c r="E91">
-        <v>-22.6420822927229</v>
+        <v>-16.03407867904222</v>
       </c>
       <c r="F91">
-        <v>-3.918404935157537</v>
+        <v>-2.045818293574044</v>
       </c>
       <c r="G91">
-        <v>-3.112690351125432</v>
+        <v>2.445295380322105</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.587020711639412</v>
       </c>
       <c r="E92">
-        <v>-24.44667465630553</v>
+        <v>-18.35803719809056</v>
       </c>
       <c r="F92">
-        <v>-4.322420426687925</v>
+        <v>-1.579308280074252</v>
       </c>
       <c r="G92">
-        <v>-3.219146303400056</v>
+        <v>2.34864699928866</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.56118258811914</v>
       </c>
       <c r="E93">
-        <v>-26.95879127037257</v>
+        <v>-21.66168125548429</v>
       </c>
       <c r="F93">
-        <v>-4.458787096904183</v>
+        <v>-1.156800314643767</v>
       </c>
       <c r="G93">
-        <v>-3.794751314244087</v>
+        <v>1.578629611047531</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.580303114828031</v>
       </c>
       <c r="E94">
-        <v>-28.97152135629574</v>
+        <v>-23.02113820953495</v>
       </c>
       <c r="F94">
-        <v>-4.129773646758067</v>
+        <v>-2.087285537390784</v>
       </c>
       <c r="G94">
-        <v>-3.32241947076202</v>
+        <v>1.864407602767369</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-6.654030632894748</v>
       </c>
       <c r="E95">
-        <v>-30.29752420861473</v>
+        <v>-27.23932117819973</v>
       </c>
       <c r="F95">
-        <v>-4.385422737875245</v>
+        <v>-2.297955935270755</v>
       </c>
       <c r="G95">
-        <v>-3.588175448526125</v>
+        <v>1.385697064573741</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-6.790041252031232</v>
       </c>
       <c r="E96">
-        <v>-34.21277264429941</v>
+        <v>-29.39487933432483</v>
       </c>
       <c r="F96">
-        <v>-4.132083135077072</v>
+        <v>-2.326064097982548</v>
       </c>
       <c r="G96">
-        <v>-3.602698135148228</v>
+        <v>1.757203531977191</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-6.983354358674766</v>
       </c>
       <c r="E97">
-        <v>-35.71956123595261</v>
+        <v>-31.99825602083144</v>
       </c>
       <c r="F97">
-        <v>-4.430099905377833</v>
+        <v>-2.07289762397156</v>
       </c>
       <c r="G97">
-        <v>-3.795660212616053</v>
+        <v>0.820956178313033</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-7.23569253364902</v>
       </c>
       <c r="E98">
-        <v>-38.47374742809967</v>
+        <v>-34.05297411775373</v>
       </c>
       <c r="F98">
-        <v>-4.351476241708521</v>
+        <v>-2.267731293844809</v>
       </c>
       <c r="G98">
-        <v>-4.410977847994042</v>
+        <v>1.530753307273673</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-7.525802234282974</v>
       </c>
       <c r="E99">
-        <v>-40.6107275196083</v>
+        <v>-37.39429055041728</v>
       </c>
       <c r="F99">
-        <v>-4.190666934537858</v>
+        <v>-2.588278000766911</v>
       </c>
       <c r="G99">
-        <v>-4.248212852537787</v>
+        <v>1.014928872021167</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-7.86223486905716</v>
       </c>
       <c r="E100">
-        <v>-43.05925077318562</v>
+        <v>-39.4812559107482</v>
       </c>
       <c r="F100">
-        <v>-4.342988789299437</v>
+        <v>-2.323540062506217</v>
       </c>
       <c r="G100">
-        <v>-5.114160034290841</v>
+        <v>1.306396501925081</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-8.204502195498407</v>
       </c>
       <c r="E101">
-        <v>-46.37016303136167</v>
+        <v>-42.40923587836163</v>
       </c>
       <c r="F101">
-        <v>-4.423668460862498</v>
+        <v>-2.434033505263435</v>
       </c>
       <c r="G101">
-        <v>-5.10388981080978</v>
+        <v>0.1139677750072773</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.585054281066173</v>
       </c>
       <c r="E102">
-        <v>-49.8308511709859</v>
+        <v>-46.23272158099187</v>
       </c>
       <c r="F102">
-        <v>-4.231358826465579</v>
+        <v>-2.266884702359148</v>
       </c>
       <c r="G102">
-        <v>-4.868245603296698</v>
+        <v>-0.2298779946500533</v>
       </c>
     </row>
   </sheetData>
